--- a/Verifica_Roma_2027.xlsx
+++ b/Verifica_Roma_2027.xlsx
@@ -26008,7 +26008,7 @@
       </c>
       <c r="R418" s="1" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
     </row>
@@ -26052,7 +26052,7 @@
       </c>
       <c r="R419" s="1" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
     </row>
@@ -26096,7 +26096,7 @@
       </c>
       <c r="R420" s="1" t="inlineStr">
         <is>
-          <t>03/09/2026</t>
+          <t>07/09/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Roma_2027.xlsx
+++ b/Verifica_Roma_2027.xlsx
@@ -26008,7 +26008,7 @@
       </c>
       <c r="R418" s="1" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
     </row>
@@ -26047,12 +26047,12 @@
       <c r="P419" s="1" t="inlineStr"/>
       <c r="Q419" s="1" t="inlineStr">
         <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R419" s="1" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
     </row>
@@ -26096,7 +26096,7 @@
       </c>
       <c r="R420" s="1" t="inlineStr">
         <is>
-          <t>07/09/2026</t>
+          <t>10/09/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Roma_2027.xlsx
+++ b/Verifica_Roma_2027.xlsx
@@ -25965,50 +25965,39 @@
       </c>
     </row>
     <row r="418">
-      <c r="A418" s="1" t="inlineStr">
+      <c r="A418" t="inlineStr">
         <is>
           <t>Da Antonio</t>
         </is>
       </c>
-      <c r="B418" s="1" t="inlineStr">
+      <c r="B418" t="inlineStr">
         <is>
           <t>Via Mario Lizzani, 21</t>
         </is>
       </c>
-      <c r="C418" s="1" t="inlineStr">
+      <c r="C418" t="inlineStr">
         <is>
           <t>391/7475549</t>
         </is>
       </c>
-      <c r="D418" s="1" t="inlineStr"/>
-      <c r="E418" s="1" t="inlineStr"/>
-      <c r="F418" s="1" t="inlineStr"/>
-      <c r="G418" s="1" t="inlineStr"/>
-      <c r="H418" s="1" t="inlineStr"/>
-      <c r="I418" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J418" s="1" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="K418" s="1" t="inlineStr"/>
-      <c r="L418" s="1" t="inlineStr"/>
-      <c r="M418" s="1" t="inlineStr"/>
-      <c r="N418" s="1" t="inlineStr"/>
-      <c r="O418" s="1" t="inlineStr"/>
-      <c r="P418" s="1" t="inlineStr"/>
-      <c r="Q418" s="1" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R418" s="1" t="inlineStr">
-        <is>
-          <t>10/09/2026</t>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J418" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q418" t="inlineStr">
+        <is>
+          <t>Trovato online con menzione recente | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R418" t="inlineStr">
+        <is>
+          <t>14/09/2026</t>
         </is>
       </c>
     </row>
@@ -26047,12 +26036,12 @@
       <c r="P419" s="1" t="inlineStr"/>
       <c r="Q419" s="1" t="inlineStr">
         <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Err SerpAPI: HTTPSConnectionPool(host='serpapi.com',  | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R419" s="1" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
     </row>
@@ -26096,7 +26085,7 @@
       </c>
       <c r="R420" s="1" t="inlineStr">
         <is>
-          <t>10/09/2026</t>
+          <t>14/09/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Roma_2027.xlsx
+++ b/Verifica_Roma_2027.xlsx
@@ -26036,12 +26036,12 @@
       <c r="P419" s="1" t="inlineStr"/>
       <c r="Q419" s="1" t="inlineStr">
         <is>
-          <t>Err SerpAPI: HTTPSConnectionPool(host='serpapi.com',  | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R419" s="1" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
     </row>
@@ -26085,7 +26085,7 @@
       </c>
       <c r="R420" s="1" t="inlineStr">
         <is>
-          <t>14/09/2026</t>
+          <t>17/09/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Roma_2027.xlsx
+++ b/Verifica_Roma_2027.xlsx
@@ -26036,12 +26036,12 @@
       <c r="P419" s="1" t="inlineStr"/>
       <c r="Q419" s="1" t="inlineStr">
         <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>Err SerpAPI: HTTPSConnectionPool(host='serpapi.com',  | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R419" s="1" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
     </row>
@@ -26085,7 +26085,7 @@
       </c>
       <c r="R420" s="1" t="inlineStr">
         <is>
-          <t>17/09/2026</t>
+          <t>21/09/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Roma_2027.xlsx
+++ b/Verifica_Roma_2027.xlsx
@@ -26036,56 +26036,49 @@
       <c r="P419" s="1" t="inlineStr"/>
       <c r="Q419" s="1" t="inlineStr">
         <is>
-          <t>Err SerpAPI: HTTPSConnectionPool(host='serpapi.com',  | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
       <c r="R419" s="1" t="inlineStr">
         <is>
-          <t>21/09/2026</t>
+          <t>24/09/2026</t>
         </is>
       </c>
     </row>
     <row r="420">
-      <c r="A420" s="1" t="inlineStr">
+      <c r="A420" t="inlineStr">
         <is>
           <t>Retrò</t>
         </is>
       </c>
-      <c r="B420" s="1" t="inlineStr">
+      <c r="B420" t="inlineStr">
         <is>
           <t>Via Baldo degli Ubaldi, 118</t>
         </is>
       </c>
-      <c r="C420" s="1" t="inlineStr">
+      <c r="C420" t="inlineStr">
         <is>
           <t>06/6636288</t>
         </is>
       </c>
-      <c r="D420" s="1" t="inlineStr"/>
-      <c r="E420" s="1" t="inlineStr"/>
-      <c r="F420" s="1" t="inlineStr"/>
-      <c r="G420" s="1" t="inlineStr"/>
-      <c r="H420" s="1" t="inlineStr"/>
-      <c r="I420" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J420" s="1" t="inlineStr"/>
-      <c r="K420" s="1" t="inlineStr"/>
-      <c r="L420" s="1" t="inlineStr"/>
-      <c r="M420" s="1" t="inlineStr"/>
-      <c r="N420" s="1" t="inlineStr"/>
-      <c r="O420" s="1" t="inlineStr"/>
-      <c r="P420" s="1" t="inlineStr"/>
-      <c r="Q420" s="1" t="inlineStr">
-        <is>
-          <t>Err SerpAPI: unhashable type: 'slice' | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R420" s="1" t="inlineStr">
-        <is>
-          <t>21/09/2026</t>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J420" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q420" t="inlineStr">
+        <is>
+          <t>Trovato online con menzione recente | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R420" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Roma_2027.xlsx
+++ b/Verifica_Roma_2027.xlsx
@@ -26002,83 +26002,83 @@
       </c>
     </row>
     <row r="419">
-      <c r="A419" s="1" t="inlineStr">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>Retrò</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>Via Baldo degli Ubaldi, 118</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>06/6636288</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J419" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q419" t="inlineStr">
+        <is>
+          <t>Trovato online con menzione recente | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R419" t="inlineStr">
+        <is>
+          <t>24/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" s="1" t="inlineStr">
         <is>
           <t>Slow</t>
         </is>
       </c>
-      <c r="B419" s="1" t="inlineStr">
+      <c r="B420" s="1" t="inlineStr">
         <is>
           <t>Corso Vittorio Emanuele II, 73</t>
         </is>
       </c>
-      <c r="C419" s="1" t="inlineStr"/>
-      <c r="D419" s="1" t="inlineStr"/>
-      <c r="E419" s="1" t="inlineStr"/>
-      <c r="F419" s="1" t="inlineStr"/>
-      <c r="G419" s="1" t="inlineStr"/>
-      <c r="H419" s="1" t="inlineStr"/>
-      <c r="I419" s="1" t="inlineStr">
+      <c r="C420" s="1" t="inlineStr"/>
+      <c r="D420" s="1" t="inlineStr"/>
+      <c r="E420" s="1" t="inlineStr"/>
+      <c r="F420" s="1" t="inlineStr"/>
+      <c r="G420" s="1" t="inlineStr"/>
+      <c r="H420" s="1" t="inlineStr"/>
+      <c r="I420" s="1" t="inlineStr">
         <is>
           <t>INCERTO</t>
         </is>
       </c>
-      <c r="J419" s="1" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="K419" s="1" t="inlineStr"/>
-      <c r="L419" s="1" t="inlineStr"/>
-      <c r="M419" s="1" t="inlineStr"/>
-      <c r="N419" s="1" t="inlineStr"/>
-      <c r="O419" s="1" t="inlineStr"/>
-      <c r="P419" s="1" t="inlineStr"/>
-      <c r="Q419" s="1" t="inlineStr">
+      <c r="J420" s="1" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="K420" s="1" t="inlineStr"/>
+      <c r="L420" s="1" t="inlineStr"/>
+      <c r="M420" s="1" t="inlineStr"/>
+      <c r="N420" s="1" t="inlineStr"/>
+      <c r="O420" s="1" t="inlineStr"/>
+      <c r="P420" s="1" t="inlineStr"/>
+      <c r="Q420" s="1" t="inlineStr">
         <is>
           <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
         </is>
       </c>
-      <c r="R419" s="1" t="inlineStr">
-        <is>
-          <t>24/09/2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="420">
-      <c r="A420" t="inlineStr">
-        <is>
-          <t>Retrò</t>
-        </is>
-      </c>
-      <c r="B420" t="inlineStr">
-        <is>
-          <t>Via Baldo degli Ubaldi, 118</t>
-        </is>
-      </c>
-      <c r="C420" t="inlineStr">
-        <is>
-          <t>06/6636288</t>
-        </is>
-      </c>
-      <c r="I420" t="inlineStr">
-        <is>
-          <t>APERTO</t>
-        </is>
-      </c>
-      <c r="J420" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="Q420" t="inlineStr">
-        <is>
-          <t>Trovato online con menzione recente | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R420" t="inlineStr">
-        <is>
-          <t>24/09/2026</t>
+      <c r="R420" s="1" t="inlineStr">
+        <is>
+          <t>28/09/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Roma_2027.xlsx
+++ b/Verifica_Roma_2027.xlsx
@@ -26078,7 +26078,7 @@
       </c>
       <c r="R420" s="1" t="inlineStr">
         <is>
-          <t>28/09/2026</t>
+          <t>01/10/2026</t>
         </is>
       </c>
     </row>

--- a/Verifica_Roma_2027.xlsx
+++ b/Verifica_Roma_2027.xlsx
@@ -26,18 +26,12 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFF00"/>
-        <bgColor rgb="00FFFF00"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -52,9 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -26039,46 +26032,34 @@
       </c>
     </row>
     <row r="420">
-      <c r="A420" s="1" t="inlineStr">
+      <c r="A420" t="inlineStr">
         <is>
           <t>Slow</t>
         </is>
       </c>
-      <c r="B420" s="1" t="inlineStr">
+      <c r="B420" t="inlineStr">
         <is>
           <t>Corso Vittorio Emanuele II, 73</t>
         </is>
       </c>
-      <c r="C420" s="1" t="inlineStr"/>
-      <c r="D420" s="1" t="inlineStr"/>
-      <c r="E420" s="1" t="inlineStr"/>
-      <c r="F420" s="1" t="inlineStr"/>
-      <c r="G420" s="1" t="inlineStr"/>
-      <c r="H420" s="1" t="inlineStr"/>
-      <c r="I420" s="1" t="inlineStr">
-        <is>
-          <t>INCERTO</t>
-        </is>
-      </c>
-      <c r="J420" s="1" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="K420" s="1" t="inlineStr"/>
-      <c r="L420" s="1" t="inlineStr"/>
-      <c r="M420" s="1" t="inlineStr"/>
-      <c r="N420" s="1" t="inlineStr"/>
-      <c r="O420" s="1" t="inlineStr"/>
-      <c r="P420" s="1" t="inlineStr"/>
-      <c r="Q420" s="1" t="inlineStr">
-        <is>
-          <t>TF: non trovato | FB: nessun handle | IG: nessun handle</t>
-        </is>
-      </c>
-      <c r="R420" s="1" t="inlineStr">
-        <is>
-          <t>01/10/2026</t>
+      <c r="I420" t="inlineStr">
+        <is>
+          <t>APERTO</t>
+        </is>
+      </c>
+      <c r="J420" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="Q420" t="inlineStr">
+        <is>
+          <t>Trovato online con menzione recente | TF: non trovato | FB: nessun handle | IG: nessun handle</t>
+        </is>
+      </c>
+      <c r="R420" t="inlineStr">
+        <is>
+          <t>05/10/2026</t>
         </is>
       </c>
     </row>
